--- a/data/appointments.xlsx
+++ b/data/appointments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +528,70 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>APT-20251213011651-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-12-13 01:16:51</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>محمد احمد</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>محمد عبدالفتاح زكي عبدالفتاح</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>APT-20251213020608-3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-12-13 02:06:08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>محمد احمد</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/appointments.xlsx
+++ b/data/appointments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,94 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>APT-20251214124020-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-12-14 12:40:20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>محمد عبدالفتاح زكي عبدالفتاح</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>APT-20251214133848-5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-12-14 13:38:48</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>محمد احمد</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0123454544</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>محمد عبدالفتاح زكي عبدالفتاح</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>القلب</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AHJ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>حجز من خلال المساعد الآلي</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
